--- a/Data/Home/BedroomOne.Window001.xlsx
+++ b/Data/Home/BedroomOne.Window001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1710022296</v>
+        <v>1712014797</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1710061381</v>
+        <v>1712064042</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1710540363</v>
+        <v>1712101345</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1710581947</v>
+        <v>1712153445</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1710626727</v>
+        <v>1712187826</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1710660422</v>
+        <v>1712230487</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1710799645</v>
+        <v>1712533267</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +732,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1710838473</v>
+        <v>1712573031</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1711059180</v>
+        <v>1712705895</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +806,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1711101396</v>
+        <v>1712767340</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,6 +843,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +862,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1711410364</v>
+        <v>1713310492</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +880,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +899,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1711464290</v>
+        <v>1713359024</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +917,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +936,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1711517405</v>
+        <v>1713396598</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +954,266 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Window_Operation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1713450900</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BedroomOne.Window001.state: close</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Window_Operation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1713483449</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>BedroomOne.Window001.state: open</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Window_Operation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1713533201</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BedroomOne.Window001.state: close</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Window_Operation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1713590703</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>BedroomOne.Window001.state: open</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Window_Operation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1713783736</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BedroomOne.Window001.state: close</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Window_Operation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1714001563</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BedroomOne.Window001.state: open</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Window_Operation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BedroomOne</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1714046313</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>BedroomOne.Window001.state: close</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
